--- a/out/LSTM-S4_repeat_1_000007.xlsx
+++ b/out/LSTM-S4_repeat_1_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.295895168639794</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.295895168639794</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.295895168639794</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.668078547550069</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6958951686397941</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.268078547550068</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002272045249613002</v>
+        <v>-6.350885619758629e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.619332613233365</v>
+        <v>0.7321632397323752</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.242714241979119</v>
+        <v>1.46545842325624</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3927805869190416</v>
+        <v>0.1097911438137972</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.405427343352351</v>
+        <v>0.9518947012812844</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4911035361867141</v>
+        <v>0.1372747102358227</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.994916273306048</v>
+        <v>1.116670368164936</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7039945901134305</v>
+        <v>0.1967826461112384</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.91207928099512</v>
+        <v>1.373038420346467</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7531347643242808</v>
+        <v>0.2105184526747808</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.714407079428359</v>
+        <v>1.597307351345162</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7981710488413163</v>
+        <v>0.2231063901292494</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.557672183030884</v>
+        <v>1.833019085469454</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3601997493385982</v>
+        <v>0.1006837643598522</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.479237211912401</v>
+        <v>1.811094679552205</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.173960015445816</v>
+        <v>0.04862565627917254</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.668078547550069</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.466675002174386</v>
+        <v>1.807583232453053</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08288676824058588</v>
+        <v>0.02316867753908389</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.45835031421514</v>
+        <v>1.805256255114777</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0245591344490661</v>
+        <v>0.006862180623952113</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.424492297707091</v>
+        <v>1.795788932819602</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01624489908671326</v>
+        <v>0.004536897260261469</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.432410190626672</v>
+        <v>1.797998640916994</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.008311388652560961</v>
+        <v>0.002320085942499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.432779389050185</v>
+        <v>1.798098252506395</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004249154192906999</v>
+        <v>0.00118386798434055</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.432961384338904</v>
+        <v>1.79814552668101</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00159429783000765</v>
+        <v>0.0004423189860551449</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.431897352753059</v>
+        <v>1.79784438854966</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008670313179623429</v>
+        <v>0.0002383767632912877</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.432035469328276</v>
+        <v>1.797879399410737</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004146174138947974</v>
+        <v>0.0001126200326826326</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.431997916647768</v>
+        <v>1.797865283292404</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002547641510028506</v>
+        <v>6.781267869019299e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.432092820770928</v>
+        <v>1.797888233616753</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001308767287880796</v>
+        <v>3.308665882696171e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.432099704621044</v>
+        <v>1.797886551950965</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.094014663182173e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.432090592807619</v>
+        <v>1.797880408501921</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.721183046616949e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.43210432768306</v>
+        <v>1.797880721933198</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.432095438776742</v>
+        <v>1.797874578137222</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.432088109858052</v>
+        <v>1.797868893603194</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.432083854679882</v>
+        <v>1.79786414232798</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.432078132400851</v>
+        <v>1.797858853180418</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.432073063045483</v>
+        <v>1.797858830446117</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.432068698071514</v>
+        <v>1.797859148726333</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.43206978931797</v>
+        <v>1.797860239972791</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.432069099710835</v>
+        <v>1.797859550365655</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.432069130023236</v>
+        <v>1.797859580678056</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.432068940570726</v>
+        <v>1.797859391225546</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.432068993617429</v>
+        <v>1.797859444272249</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.432069046664131</v>
+        <v>1.797859497318952</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.432069008773629</v>
+        <v>1.79785945942845</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.432068879945922</v>
+        <v>1.797859330600743</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.432068735962016</v>
+        <v>1.797859186616836</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.432068576821908</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.43206862986861</v>
+        <v>1.79785908052343</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.432068576821908</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.432068576821908</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.432068394947498</v>
+        <v>1.797858845602318</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.432068561665706</v>
+        <v>1.797859012320526</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.432068758696317</v>
+        <v>1.797859209351137</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.432068599556208</v>
+        <v>1.797859050211029</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.43206863744671</v>
+        <v>1.79785908810153</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.43206883447732</v>
+        <v>1.797859285132141</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.43206881174302</v>
+        <v>1.79785926239784</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.432068660181011</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.432068584400008</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.432068682915313</v>
+        <v>1.797859133570133</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.432068690493414</v>
+        <v>1.797859141148233</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.432068955726927</v>
+        <v>1.797859406381747</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.432068660181011</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.432068902680224</v>
+        <v>1.797859353335044</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.432068986039329</v>
+        <v>1.797859436694148</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.43206881932112</v>
+        <v>1.79785926997594</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.432069008773629</v>
+        <v>1.79785945942845</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.432068660181011</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.432068455572301</v>
+        <v>1.797858906227121</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.432068569243806</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.432068584400008</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.432068349478896</v>
+        <v>1.797858800133715</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.432068410103699</v>
+        <v>1.797858860758518</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.432068281275991</v>
+        <v>1.797858731930812</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.432068417681799</v>
+        <v>1.797858868336619</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.432068591978108</v>
+        <v>1.797859042632928</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.432068735962016</v>
+        <v>1.797859186616836</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.432068569243806</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.432068561665706</v>
+        <v>1.797859012320526</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.432068273697891</v>
+        <v>1.797858724352711</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.432068288854093</v>
+        <v>1.797858739508913</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.432068516197104</v>
+        <v>1.797858966851924</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.432068501040903</v>
+        <v>1.797858951695724</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.432068607134308</v>
+        <v>1.797859057789129</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.432068334322695</v>
+        <v>1.797858784977515</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.432068432837999</v>
+        <v>1.79785888349282</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.432068584400008</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.432068599556208</v>
+        <v>1.797859050211029</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.432068576821908</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.432068660181011</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.432068758696317</v>
+        <v>1.797859209351137</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.432068591978108</v>
+        <v>1.797859042632928</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.432068576821908</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.432068546509505</v>
+        <v>1.797858997164326</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.432068531353305</v>
+        <v>1.797858982008125</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.432068569243806</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.432068584400008</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.432068576821908</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_1_000007.xlsx
+++ b/out/LSTM-S4_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6958951686397941</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.268078547550068</v>
+        <v>0.8320598689052213</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.268078547550068</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.668078547550069</v>
+        <v>1.509539575462904</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002272045249613002</v>
+        <v>-0.000199863019320881</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.619332613233365</v>
+        <v>2.304125358357273</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.242714241979119</v>
+        <v>4.611812630251396</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3927805869190416</v>
+        <v>0.3455138983622461</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.405427343352351</v>
+        <v>2.995622463937212</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4911035361867141</v>
+        <v>0.4320047391642156</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.994916273306048</v>
+        <v>3.514173027496438</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7039945901134305</v>
+        <v>0.6192767448519119</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.91207928099512</v>
+        <v>4.320965789618051</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7531347643242808</v>
+        <v>0.6625034507870355</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.714407079428359</v>
+        <v>5.026742489828058</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7981710488413163</v>
+        <v>0.7021208618257896</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.557672183030884</v>
+        <v>5.76853019825478</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3601997493385982</v>
+        <v>0.3168534204915949</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.668078547550069</v>
+        <v>1.309539575462904</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.479237211912401</v>
+        <v>5.699534050501043</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.173960015445816</v>
+        <v>0.1530263629859659</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.668078547550069</v>
+        <v>0.6320598689052213</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.466675002174386</v>
+        <v>5.688483566834128</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08288676824058588</v>
+        <v>0.07291250607797407</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.04541983765246159</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.45835031421514</v>
+        <v>5.681160691856571</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0245591344490661</v>
+        <v>0.02160346695207557</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.424492297707091</v>
+        <v>5.651377454087689</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01624489908671326</v>
+        <v>0.01428875920848424</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.432410190626672</v>
+        <v>5.658341835279974</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.008311388652560961</v>
+        <v>0.007310706298129525</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.432779389050185</v>
+        <v>5.658666010433739</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004249154192906999</v>
+        <v>0.003737769827077194</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.432961384338904</v>
+        <v>5.658825507347446</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00159429783000765</v>
+        <v>0.001402049061043171</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.431897352753059</v>
+        <v>5.657889000095026</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008670313179623429</v>
+        <v>0.0007614305528732416</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.432035469328276</v>
+        <v>5.658009853821465</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004146174138947974</v>
+        <v>0.0003645494270096227</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.431997916647768</v>
+        <v>5.657976211963191</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002547641510028506</v>
+        <v>0.0002232775872449294</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.432092820770928</v>
+        <v>5.658059029459604</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001308767287880796</v>
+        <v>0.0001144068222683124</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.432099704621044</v>
+        <v>5.658064478354385</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.094014663182173e-05</v>
+        <v>5.294740158554031e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.432090592807619</v>
+        <v>5.658055861268357</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.721183046616949e-05</v>
+        <v>3.209524495511864e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.43210432768306</v>
+        <v>5.658067359236438</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>1.248416916455026e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.432095438776742</v>
+        <v>5.65805892784851</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>2.205584102398162e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.432088109858052</v>
+        <v>5.658051872993929</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.432083854679882</v>
+        <v>5.658047534456656</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.432078132400851</v>
+        <v>5.658041956161532</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.432073063045483</v>
+        <v>5.658036909540464</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.432068698071514</v>
+        <v>5.658037227820681</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.43206978931797</v>
+        <v>5.658038319067138</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.432069099710835</v>
+        <v>5.658037629460002</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.432069130023236</v>
+        <v>5.658037659772403</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.432068940570726</v>
+        <v>5.658037470319893</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.432068993617429</v>
+        <v>5.658037523366596</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.432069046664131</v>
+        <v>5.658037576413299</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.432069008773629</v>
+        <v>5.658037538522796</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.432068879945922</v>
+        <v>5.65803740969509</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.432068735962016</v>
+        <v>5.658037265711183</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.432068576821908</v>
+        <v>5.658037106571075</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.43206862986861</v>
+        <v>5.658037159617777</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.432068576821908</v>
+        <v>5.658037106571075</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.432068576821908</v>
+        <v>5.658037106571075</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.432068394947498</v>
+        <v>5.658036924696665</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.432068561665706</v>
+        <v>5.658037091414873</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.432068758696317</v>
+        <v>5.658037288445484</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.432068599556208</v>
+        <v>5.658037129305376</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.43206863744671</v>
+        <v>5.658037167195877</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.43206883447732</v>
+        <v>5.658037364226487</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.43206881174302</v>
+        <v>5.658037341492187</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.432068660181011</v>
+        <v>5.658037189930178</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.432068584400008</v>
+        <v>5.658037114149175</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.432068682915313</v>
+        <v>5.65803721266448</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.432068690493414</v>
+        <v>5.658037220242581</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.432068955726927</v>
+        <v>5.658037485476094</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.432068660181011</v>
+        <v>5.658037189930178</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.432068902680224</v>
+        <v>5.658037432429391</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.432068986039329</v>
+        <v>5.658037515788496</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.43206881932112</v>
+        <v>5.658037349070288</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.432069008773629</v>
+        <v>5.658037538522796</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.432068660181011</v>
+        <v>5.658037189930178</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.432068455572301</v>
+        <v>5.658036985321468</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.432068569243806</v>
+        <v>5.658037098992973</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.432068584400008</v>
+        <v>5.658037114149175</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.432068349478896</v>
+        <v>5.658036879228063</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.432068410103699</v>
+        <v>5.658036939852866</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.432068281275991</v>
+        <v>5.658036811025158</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.432068417681799</v>
+        <v>5.658036947430967</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.432068591978108</v>
+        <v>5.658037121727275</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.432068735962016</v>
+        <v>5.658037265711183</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.432068569243806</v>
+        <v>5.658037098992973</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.432068561665706</v>
+        <v>5.658037091414873</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.432068273697891</v>
+        <v>5.658036803447058</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.432068288854093</v>
+        <v>5.65803681860326</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.432068516197104</v>
+        <v>5.658037045946271</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.432068501040903</v>
+        <v>5.65803703079007</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.432068607134308</v>
+        <v>5.658037136883475</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.432068334322695</v>
+        <v>5.658036864071862</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.432068432837999</v>
+        <v>5.658036962587166</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.432068584400008</v>
+        <v>5.658037114149175</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.432068599556208</v>
+        <v>5.658037129305376</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.432068576821908</v>
+        <v>5.658037106571075</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.432068660181011</v>
+        <v>5.658037189930178</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.432068758696317</v>
+        <v>5.658037288445484</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.432068591978108</v>
+        <v>5.658037121727275</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.432068576821908</v>
+        <v>5.658037106571075</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.432068546509505</v>
+        <v>5.658037076258672</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.432068531353305</v>
+        <v>5.658037061102473</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.432068569243806</v>
+        <v>5.658037098992973</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.432068584400008</v>
+        <v>5.658037114149175</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.295895168639794</v>
+        <v>-0.7228995442101446</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.432068576821908</v>
+        <v>5.658037106571075</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_1_000007.xlsx
+++ b/out/LSTM-S4_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.003291016444563866</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.44</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001450072973966599</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.000626804307103157</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04541983765246159</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.0001535229384899139</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.6320598689052213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0003171581774950027</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>9.80868935585022e-05</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-3.196112811565399e-05</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0001008491963148117</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.8320598689052213</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0003566425293684006</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0006142649799585342</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0007584504783153534</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0008312426507472992</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.509539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001024154946208</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001287126913666725</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001498570665717125</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001558084040880203</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001558937132358551</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.509539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001577762886881828</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.309539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001770207658410072</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.309539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001943541690707207</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.309539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.00221116840839386</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.309539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002499137073755264</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.309539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.00246860459446907</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.309539575462904</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002213198691606522</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.309539575462904</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002011952921748161</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.309539575462904</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001939158886671066</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001874705776572227</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001992311328649521</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002060439437627792</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002096811309456825</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.309539575462904</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002069186419248581</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.309539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002128856256604195</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002240752801299095</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002238821238279343</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002480603754520416</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.00333729200065136</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.309539575462904</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.003240680322051048</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.309539575462904</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002730224281549454</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000199863019320881</v>
+        <v>-9.847483767673839e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.304125358357273</v>
+        <v>1.135269364744381</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002086270600557327</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.611812630251396</v>
+        <v>2.272293802601463</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3455138983622461</v>
+        <v>0.170238705425321</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001603564247488976</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>2.995622463937212</v>
+        <v>1.475978054970539</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4320047391642156</v>
+        <v>0.2128538306148102</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001009467989206314</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.514173027496438</v>
+        <v>1.73147400049498</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6192767448519119</v>
+        <v>0.3051247940730504</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0009711906313896179</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.320965789618051</v>
+        <v>2.12899020646805</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6625034507870355</v>
+        <v>0.3264230906045389</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001228004693984985</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.026742489828058</v>
+        <v>2.476734714487173</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7021208618257896</v>
+        <v>0.3459426824196715</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.001430507749319077</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.76853019825478</v>
+        <v>2.84222246969821</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3168534204915949</v>
+        <v>0.1561181643286793</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001435205340385437</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.309539575462904</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.699534050501043</v>
+        <v>2.808227162221812</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1530263629859659</v>
+        <v>0.07539793774942327</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>2.788007259368896e-05</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6320598689052213</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.688483566834128</v>
+        <v>2.802782455418609</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07291250607797407</v>
+        <v>0.0359242597025518</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0008230097591876984</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04541983765246159</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.681160691856571</v>
+        <v>2.799174387380349</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02160346695207557</v>
+        <v>0.01064272668113367</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001877931877970695</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.651377454087689</v>
+        <v>2.784497831892729</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01428875920848424</v>
+        <v>0.00703806480972186</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00237942673265934</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.658341835279974</v>
+        <v>2.787926788498571</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007310706298129525</v>
+        <v>0.003599227595164553</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.002875844016671181</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.658666010433739</v>
+        <v>2.788083974691177</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003737769827077194</v>
+        <v>0.00183920503582717</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.002852819859981537</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.658825507347446</v>
+        <v>2.788160028576574</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001402049061043171</v>
+        <v>0.0006883065841396154</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002734126523137093</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.657889000095026</v>
+        <v>2.787696039526969</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007614305528732416</v>
+        <v>0.0003728527375844399</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.002690372988581657</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.658009853821465</v>
+        <v>2.787753052196268</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0003645494270096227</v>
+        <v>0.0001769931586778572</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00265018455684185</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.657976211963191</v>
+        <v>2.78773394685101</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002232775872449294</v>
+        <v>0.0001071708833875946</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002599695697426796</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.658059029459604</v>
+        <v>2.7877721949113</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001144068222683124</v>
+        <v>5.367404197667074e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002907499670982361</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.658064478354385</v>
+        <v>2.787772352408284</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.294740158554031e-05</v>
+        <v>2.397370079277015e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.001928968355059624</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.658055861268357</v>
+        <v>2.787765559021471</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.209524495511864e-05</v>
+        <v>1.290804928867796e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.002126291394233704</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.658067359236438</v>
+        <v>2.787768668586948</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>3.15927894345679e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003355404362082481</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.65805892784851</v>
+        <v>2.787761953601076</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004324479959905148</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.658051872993929</v>
+        <v>2.787755857344634</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004758697003126144</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.658047534456656</v>
+        <v>2.787751188075997</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.005033498629927635</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.658041956161532</v>
+        <v>2.787745898928435</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004828860983252525</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.658036909540464</v>
+        <v>2.787745876194134</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.003757813945412636</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.658037227820681</v>
+        <v>2.78774619447435</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002108914777636528</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.658038319067138</v>
+        <v>2.787747285720807</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002674143761396408</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.658037629460002</v>
+        <v>2.787746596113672</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.004479319788515568</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.658037659772403</v>
+        <v>2.787746626426073</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.005995779298245907</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.658037470319893</v>
+        <v>2.787746436973563</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006819195114076138</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.658037523366596</v>
+        <v>2.787746490020266</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00740065798163414</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.658037576413299</v>
+        <v>2.787746543066969</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.007514792494475842</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.658037538522796</v>
+        <v>2.787746505176466</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.007133747451007366</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.65803740969509</v>
+        <v>2.78774637634876</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.006608748808503151</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.658037265711183</v>
+        <v>2.787746232364853</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.006271889433264732</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.658037106571075</v>
+        <v>2.787746073224744</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006121737882494926</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.658037159617777</v>
+        <v>2.787746126271447</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.006293121725320816</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.658037106571075</v>
+        <v>2.787746073224744</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.00636753998696804</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.658037106571075</v>
+        <v>2.787746073224744</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.006327005103230476</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.658036924696665</v>
+        <v>2.787745891350335</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.00626660417765379</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.658037091414873</v>
+        <v>2.787746058068543</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006557203829288483</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.658037288445484</v>
+        <v>2.787746255099154</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00675564631819725</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.658037129305376</v>
+        <v>2.787746095959045</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.006594223901629448</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.658037167195877</v>
+        <v>2.787746133849547</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.006444971077144146</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.658037364226487</v>
+        <v>2.787746330880158</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.006714825518429279</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.658037341492187</v>
+        <v>2.787746308145857</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.007039953023195267</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.658037189930178</v>
+        <v>2.787746156583848</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.007008804939687252</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.658037114149175</v>
+        <v>2.787746080802844</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.006792766973376274</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.65803721266448</v>
+        <v>2.787746179318149</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.006308617070317268</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.658037220242581</v>
+        <v>2.78774618689625</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006031040102243423</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.658037485476094</v>
+        <v>2.787746452129764</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.005988915450870991</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.658037189930178</v>
+        <v>2.787746156583848</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005681058391928673</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.658037432429391</v>
+        <v>2.787746399083061</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.005514062009751797</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.658037515788496</v>
+        <v>2.787746482442165</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.004613485187292099</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.658037349070288</v>
+        <v>2.787746315723957</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.004485382698476315</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.658037538522796</v>
+        <v>2.787746505176466</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004813937470316887</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.658037189930178</v>
+        <v>2.787746156583848</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.005387701094150543</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.658036985321468</v>
+        <v>2.787745951975138</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.005695736035704613</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.658037098992973</v>
+        <v>2.787746065646644</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005612565204501152</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.658037114149175</v>
+        <v>2.787746080802844</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005393307656049728</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.658036879228063</v>
+        <v>2.787745845881732</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005145741626620293</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.658036939852866</v>
+        <v>2.787745906506535</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004925536923110485</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.658036811025158</v>
+        <v>2.787745777678829</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.004139319062232971</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.658036947430967</v>
+        <v>2.787745914084636</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003882601857185364</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.658037121727275</v>
+        <v>2.787746088380945</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004010382108390331</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.658037265711183</v>
+        <v>2.787746232364853</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.004093705676496029</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.658037098992973</v>
+        <v>2.787746065646644</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004284059628844261</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.658037091414873</v>
+        <v>2.787746058068543</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.004719956777989864</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.658036803447058</v>
+        <v>2.787745770100728</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004873600788414478</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.65803681860326</v>
+        <v>2.787745785256929</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004804255440831184</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.658037045946271</v>
+        <v>2.787746012599941</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004459479823708534</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.65803703079007</v>
+        <v>2.78774599744374</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004363369196653366</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.658037136883475</v>
+        <v>2.787746103537145</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004335921257734299</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.658036864071862</v>
+        <v>2.787745830725532</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004138505086302757</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.658036962587166</v>
+        <v>2.787745929240837</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003886888734996319</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.658037114149175</v>
+        <v>2.787746080802844</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003708599135279655</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.658037129305376</v>
+        <v>2.787746095959045</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003537777811288834</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.658037106571075</v>
+        <v>2.787746073224744</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003366004675626755</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.658037189930178</v>
+        <v>2.787746156583848</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003488535061478615</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.658037288445484</v>
+        <v>2.787746255099154</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.00371067225933075</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.658037121727275</v>
+        <v>2.787746088380945</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003756859339773655</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.658037106571075</v>
+        <v>2.787746073224744</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003614597953855991</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.658037076258672</v>
+        <v>2.787746042912342</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003417480736970901</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7228995442101446</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.658037061102473</v>
+        <v>2.787746027756142</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003274636343121529</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.658037098992973</v>
+        <v>2.787746065646644</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003147317096590996</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7228995442101446</v>
+        <v>0.3299999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.658037114149175</v>
+        <v>2.787746080802844</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002950083464384079</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7228995442101446</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.658037106571075</v>
+        <v>2.787746073224744</v>
       </c>
     </row>
   </sheetData>
